--- a/users.xlsx
+++ b/users.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HDUT\Desktop\測試LINE-BOT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HDUT\Desktop\LINE官方API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84785EF8-360F-4DF5-8E66-3A5EB79439B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C8C34C-EF63-4DB2-BAAC-FF40AD02EAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>編號</t>
   </si>
@@ -32,12 +32,6 @@
   </si>
   <si>
     <t>明書-Minh Thư</t>
-  </si>
-  <si>
-    <t>U70cb26d7b3947c5e23771e70ac358cf6</t>
-  </si>
-  <si>
-    <t>冠Ming</t>
   </si>
 </sst>
 </file>
@@ -362,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="38.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -381,14 +375,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
